--- a/mlef_pipeline/results/DCR/HIGH_PDL1/RWD_PYRAD/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/DCR/HIGH_PDL1/RWD_PYRAD/rwd-only/results.xlsx
@@ -473,17 +473,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.37 ± 0.15</t>
+          <t>0.34 ± 0.13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.44 ± 0.43</t>
+          <t>0.42 ± 0.44</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.65 ± 0.45</t>
+          <t>0.64 ± 0.47</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,22 +498,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.45 ± 0.22</t>
+          <t>0.41 ± 0.22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -528,22 +528,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.51 ± 0.21</t>
+          <t>0.53 ± 0.22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="F4" t="n">
